--- a/demo/output_statistics/UIKit3.1_bug统计报表.xlsx
+++ b/demo/output_statistics/UIKit3.1_bug统计报表.xlsx
@@ -558,7 +558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UIKit3.1_2025-06-16 17:32:03_bug统计报表</t>
+          <t>UIKit3.1_2025-06-17 17:39:02_bug统计报表</t>
         </is>
       </c>
     </row>
